--- a/lawyer_forms/010_copyright_request_form--lawyer_forms.xlsx
+++ b/lawyer_forms/010_copyright_request_form--lawyer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -839,12 +839,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>contact_state</t>
+          <t>contact_state_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Contact State 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -862,12 +862,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>contact_country</t>
+          <t>contact_country_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Contact Country 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -940,7 +940,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Contact Phone2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1129,7 +1129,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1222,7 +1222,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>contact_state_choices</t>
+          <t>contact_state_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>contact_state_choices</t>
+          <t>contact_state_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1256,7 +1256,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>contact_country_choices</t>
+          <t>contact_country_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>contact_country_choices</t>
+          <t>contact_country_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
